--- a/exercices/exercice_indices_prix.xlsx
+++ b/exercices/exercice_indices_prix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF831A0-D72E-4F55-9615-6C276008D844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E80720-9E04-493F-90D8-6BF6D0D397C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{4B094D14-38C3-40CB-84C2-D4E41A726E94}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{4B094D14-38C3-40CB-84C2-D4E41A726E94}"/>
   </bookViews>
   <sheets>
     <sheet name="EXERCICE" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Understanding national accounts (ocde), exercice 1 chapitre 2</t>
   </si>
@@ -484,14 +484,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -499,23 +505,17 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -631,8 +631,8 @@
       <xdr:rowOff>394965</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="779317" cy="470943"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="ZoneTexte 15">
@@ -894,7 +894,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="16" name="ZoneTexte 15">
@@ -965,8 +965,8 @@
       <xdr:rowOff>153939</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="779317" cy="470943"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="ZoneTexte 16">
@@ -1216,7 +1216,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="ZoneTexte 16">
@@ -1286,7 +1286,7 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>231385</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2107243" cy="418778"/>
+    <xdr:ext cx="3116532" cy="418778"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
@@ -1303,7 +1303,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="13085493" y="2155435"/>
-              <a:ext cx="2107243" cy="418778"/>
+              <a:ext cx="3116532" cy="418778"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1330,13 +1330,12 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:f>
                     <m:fPr>
                       <m:ctrlPr>
-                        <a:rPr lang="fr-CH" sz="1100" i="1">
+                        <a:rPr lang="fr-CH" sz="1400" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
                       </m:ctrlPr>
@@ -1346,7 +1345,7 @@
                         <m:naryPr>
                           <m:chr m:val="∑"/>
                           <m:ctrlPr>
-                            <a:rPr lang="fr-CH" sz="1100" i="1">
+                            <a:rPr lang="fr-CH" sz="1400" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                           </m:ctrlPr>
@@ -1356,13 +1355,13 @@
                             <m:rPr>
                               <m:brk m:alnAt="23"/>
                             </m:rPr>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>𝑖</m:t>
                           </m:r>
                           <m:r>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>=1</m:t>
@@ -1370,7 +1369,7 @@
                         </m:sub>
                         <m:sup>
                           <m:r>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>𝑘</m:t>
@@ -1380,14 +1379,14 @@
                           <m:sSub>
                             <m:sSubPr>
                               <m:ctrlPr>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑝</m:t>
@@ -1395,13 +1394,13 @@
                             </m:e>
                             <m:sub>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>=2</m:t>
@@ -1411,14 +1410,14 @@
                           <m:sSub>
                             <m:sSubPr>
                               <m:ctrlPr>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑞</m:t>
@@ -1426,13 +1425,13 @@
                             </m:e>
                             <m:sub>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>=1</m:t>
@@ -1447,7 +1446,7 @@
                         <m:naryPr>
                           <m:chr m:val="∑"/>
                           <m:ctrlPr>
-                            <a:rPr lang="fr-CH" sz="1100" i="1">
+                            <a:rPr lang="fr-CH" sz="1400" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                           </m:ctrlPr>
@@ -1457,13 +1456,13 @@
                             <m:rPr>
                               <m:brk m:alnAt="23"/>
                             </m:rPr>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>𝑖</m:t>
                           </m:r>
                           <m:r>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>=1</m:t>
@@ -1471,7 +1470,7 @@
                         </m:sub>
                         <m:sup>
                           <m:r>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>𝑘</m:t>
@@ -1481,14 +1480,14 @@
                           <m:sSub>
                             <m:sSubPr>
                               <m:ctrlPr>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑝</m:t>
@@ -1496,13 +1495,13 @@
                             </m:e>
                             <m:sub>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>=1</m:t>
@@ -1512,14 +1511,14 @@
                           <m:sSub>
                             <m:sSubPr>
                               <m:ctrlPr>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑞</m:t>
@@ -1527,13 +1526,13 @@
                             </m:e>
                             <m:sub>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1400" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>=1</m:t>
@@ -1547,10 +1546,10 @@
                 </m:oMath>
               </a14:m>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:rPr lang="fr-CH" sz="1400"/>
                 <a:t> *100 = IC(L)_2/1</a:t>
               </a:r>
-              <a:endParaRPr lang="LID4096" sz="1100"/>
+              <a:endParaRPr lang="LID4096" sz="1400"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1570,7 +1569,7 @@
           <xdr:spPr>
             <a:xfrm>
               <a:off x="13085493" y="2155435"/>
-              <a:ext cx="2107243" cy="418778"/>
+              <a:ext cx="3116532" cy="418778"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1597,24 +1596,23 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100" i="0">
+                <a:rPr lang="fr-CH" sz="1400" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>(∑</a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100" b="0" i="0">
+                <a:rPr lang="fr-CH" sz="1400" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>_(𝑖=1)^𝑘▒〖𝑝_(𝑖𝑡=2) 𝑞_(𝑖𝑡=1) 〗)/(∑_(𝑖=1)^𝑘▒〖𝑝_(𝑖𝑡=1) 𝑞_(𝑖𝑡=1) 〗)</a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:rPr lang="fr-CH" sz="1400"/>
                 <a:t> *100 = IC(L)_2/1</a:t>
               </a:r>
-              <a:endParaRPr lang="LID4096" sz="1100"/>
+              <a:endParaRPr lang="LID4096" sz="1400"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1625,11 +1623,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1090851</xdr:colOff>
+      <xdr:colOff>1097201</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>82138</xdr:rowOff>
+      <xdr:rowOff>88488</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2107243" cy="418778"/>
+    <xdr:ext cx="3011249" cy="749712"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
@@ -1645,8 +1643,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12752626" y="3028538"/>
-              <a:ext cx="2107243" cy="418778"/>
+              <a:off x="12755801" y="3031713"/>
+              <a:ext cx="3011249" cy="749712"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1673,13 +1671,12 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:f>
                     <m:fPr>
                       <m:ctrlPr>
-                        <a:rPr lang="fr-CH" sz="1100" i="1">
+                        <a:rPr lang="fr-CH" sz="1600" i="1">
                           <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                         </a:rPr>
                       </m:ctrlPr>
@@ -1689,7 +1686,7 @@
                         <m:naryPr>
                           <m:chr m:val="∑"/>
                           <m:ctrlPr>
-                            <a:rPr lang="fr-CH" sz="1100" i="1">
+                            <a:rPr lang="fr-CH" sz="1600" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                           </m:ctrlPr>
@@ -1699,13 +1696,13 @@
                             <m:rPr>
                               <m:brk m:alnAt="23"/>
                             </m:rPr>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>𝑖</m:t>
                           </m:r>
                           <m:r>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>=1</m:t>
@@ -1713,7 +1710,7 @@
                         </m:sub>
                         <m:sup>
                           <m:r>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>𝑘</m:t>
@@ -1723,14 +1720,14 @@
                           <m:sSub>
                             <m:sSubPr>
                               <m:ctrlPr>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑝</m:t>
@@ -1738,13 +1735,13 @@
                             </m:e>
                             <m:sub>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>=3</m:t>
@@ -1754,14 +1751,14 @@
                           <m:sSub>
                             <m:sSubPr>
                               <m:ctrlPr>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑞</m:t>
@@ -1769,13 +1766,13 @@
                             </m:e>
                             <m:sub>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>=2</m:t>
@@ -1790,7 +1787,7 @@
                         <m:naryPr>
                           <m:chr m:val="∑"/>
                           <m:ctrlPr>
-                            <a:rPr lang="fr-CH" sz="1100" i="1">
+                            <a:rPr lang="fr-CH" sz="1600" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                           </m:ctrlPr>
@@ -1800,13 +1797,13 @@
                             <m:rPr>
                               <m:brk m:alnAt="23"/>
                             </m:rPr>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>𝑖</m:t>
                           </m:r>
                           <m:r>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>=1</m:t>
@@ -1814,7 +1811,7 @@
                         </m:sub>
                         <m:sup>
                           <m:r>
-                            <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                            <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                               <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             </a:rPr>
                             <m:t>𝑘</m:t>
@@ -1824,14 +1821,14 @@
                           <m:sSub>
                             <m:sSubPr>
                               <m:ctrlPr>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑝</m:t>
@@ -1839,13 +1836,13 @@
                             </m:e>
                             <m:sub>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>=2</m:t>
@@ -1855,14 +1852,14 @@
                           <m:sSub>
                             <m:sSubPr>
                               <m:ctrlPr>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑞</m:t>
@@ -1870,13 +1867,13 @@
                             </m:e>
                             <m:sub>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
-                                <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
+                                <a:rPr lang="fr-CH" sz="1600" b="0" i="1">
                                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                                 </a:rPr>
                                 <m:t>=2</m:t>
@@ -1890,11 +1887,11 @@
                 </m:oMath>
               </a14:m>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:rPr lang="fr-CH" sz="1600"/>
                 <a:t> *</a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100">
+                <a:rPr lang="fr-CH" sz="1600">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -1906,10 +1903,10 @@
                 <a:t>IC(L)_2/1</a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:rPr lang="fr-CH" sz="1600"/>
                 <a:t> = IC(L)_3/1</a:t>
               </a:r>
-              <a:endParaRPr lang="LID4096" sz="1100"/>
+              <a:endParaRPr lang="LID4096" sz="1600"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -1928,8 +1925,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12752626" y="3028538"/>
-              <a:ext cx="2107243" cy="418778"/>
+              <a:off x="12755801" y="3031713"/>
+              <a:ext cx="3011249" cy="749712"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1956,25 +1953,24 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100" i="0">
+                <a:rPr lang="fr-CH" sz="1600" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>(∑</a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100" b="0" i="0">
+                <a:rPr lang="fr-CH" sz="1600" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>_(𝑖=1)^𝑘▒〖𝑝_(𝑖𝑡=3) 𝑞_(𝑖𝑡=2) 〗)/(∑_(𝑖=1)^𝑘▒〖𝑝_(𝑖𝑡=2) 𝑞_(𝑖𝑡=2) 〗)</a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:rPr lang="fr-CH" sz="1600"/>
                 <a:t> *</a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100">
+                <a:rPr lang="fr-CH" sz="1600">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -1986,10 +1982,10 @@
                 <a:t>IC(L)_2/1</a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:rPr lang="fr-CH" sz="1600"/>
                 <a:t> = IC(L)_3/1</a:t>
               </a:r>
-              <a:endParaRPr lang="LID4096" sz="1100"/>
+              <a:endParaRPr lang="LID4096" sz="1600"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
@@ -3149,8 +3145,8 @@
       <xdr:rowOff>231385</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2107243" cy="418778"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="ZoneTexte 4">
@@ -3192,7 +3188,6 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:f>
@@ -3417,7 +3412,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="ZoneTexte 4">
@@ -3492,8 +3487,8 @@
       <xdr:rowOff>82138</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2107243" cy="418778"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="ZoneTexte 6">
@@ -3535,7 +3530,6 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:f>
@@ -3776,7 +3770,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="ZoneTexte 6">
@@ -4159,7 +4153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184D09F3-E188-48AD-8947-452FE136C29B}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.6328125" customWidth="1"/>
@@ -4292,114 +4286,111 @@
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
       <c r="J10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" ht="34.5" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
       <c r="J11" s="15"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:14" ht="46" customHeight="1">
       <c r="B12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="19"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
+        <v>17</v>
+      </c>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="B16" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
     </row>
     <row r="17" spans="2:14">
       <c r="C17" s="3"/>
@@ -4408,54 +4399,57 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
     </row>
     <row r="18" spans="2:14">
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
+      <c r="C18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14">
-      <c r="C19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="22"/>
+      <c r="B19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="17"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="31.5" customHeight="1">
       <c r="B20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="19"/>
+        <v>19</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="17"/>
       <c r="J20" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="2:14" ht="29.5" customHeight="1">
-      <c r="B21" s="5" t="s">
-        <v>19</v>
+      <c r="B21" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="19"/>
@@ -4466,8 +4460,8 @@
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="2:14" ht="45.5" customHeight="1">
-      <c r="B22" s="6" t="s">
-        <v>12</v>
+      <c r="B22" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="17"/>
@@ -4478,58 +4472,18 @@
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="2:14">
-      <c r="B23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="19"/>
-    </row>
-    <row r="24" spans="2:14">
-      <c r="B24" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="14"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="J20:J22"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
+  <mergeCells count="36">
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="G10:H10"/>
@@ -4540,6 +4494,32 @@
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="J20:J22"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4681,175 +4661,175 @@
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="16">
         <f>C5*D5+C6*D6+C7*D7</f>
         <v>430</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="18">
+      <c r="D10" s="17"/>
+      <c r="E10" s="16">
         <f>E5*F5+E6*F6+E7*F7</f>
         <v>396.25</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="18">
+      <c r="F10" s="17"/>
+      <c r="G10" s="16">
         <f>G5*H5+G6*H6+G7*H7</f>
         <v>335</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="17"/>
       <c r="J10" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" ht="34.5" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="16">
         <f>C5*D5+C6*D6+C7*D7</f>
         <v>430</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="18">
+      <c r="D11" s="17"/>
+      <c r="E11" s="16">
         <f>C5*F5+C6*F6+C7*F7</f>
         <v>577.5</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="18">
+      <c r="F11" s="17"/>
+      <c r="G11" s="16">
         <f>C5*H5+C6*H6+C7*H7</f>
         <v>497.5</v>
       </c>
-      <c r="H11" s="19"/>
+      <c r="H11" s="17"/>
       <c r="J11" s="15"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:14" ht="46" customHeight="1">
       <c r="B12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="18">
         <f>C11/C10*100</f>
         <v>100</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="16">
+      <c r="D12" s="19"/>
+      <c r="E12" s="18">
         <f>E11/C10*100</f>
         <v>134.30232558139534</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="16">
+      <c r="F12" s="19"/>
+      <c r="G12" s="18">
         <f>G11/C10*100</f>
         <v>115.69767441860466</v>
       </c>
-      <c r="H12" s="17"/>
+      <c r="H12" s="19"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="16">
         <f>E5*D5+E6*D6+E7*D7</f>
         <v>379</v>
       </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="18">
+      <c r="D13" s="17"/>
+      <c r="E13" s="16">
         <f>E5*F5+E6*F6+E7*F7</f>
         <v>396.25</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="18">
+      <c r="F13" s="17"/>
+      <c r="G13" s="16">
         <f>E5*H5+E6*H6+E7*H7</f>
         <v>326.25</v>
       </c>
-      <c r="H13" s="19"/>
+      <c r="H13" s="17"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="20">
         <f>C13/E13*100</f>
         <v>95.646687697160885</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21">
+      <c r="D14" s="20"/>
+      <c r="E14" s="20">
         <f>E13/E13*100</f>
         <v>100</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21">
+      <c r="F14" s="20"/>
+      <c r="G14" s="20">
         <f>G13/E13*100</f>
         <v>82.33438485804416</v>
       </c>
-      <c r="H14" s="21"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
+      <c r="H14" s="20"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20">
+      <c r="D15" s="21"/>
+      <c r="E15" s="21">
         <f>F5*C5+F6*C6+F7*C7</f>
         <v>577.5</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20">
+      <c r="F15" s="21"/>
+      <c r="G15" s="21">
         <f>H5*E5+H6*E6+H7*E7</f>
         <v>326.25</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
+      <c r="H15" s="21"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:14">
       <c r="B16" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="21">
         <v>100</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20">
+      <c r="D16" s="21"/>
+      <c r="E16" s="21">
         <f>((F5*C5+F6*C6+F7*C7)/(D5*C5+D6*C6+D7*C7))*100</f>
         <v>134.30232558139534</v>
       </c>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20">
+      <c r="F16" s="21"/>
+      <c r="G16" s="21">
         <f>(H5*E5+H6*E6+H7*E7)/(F5*E5+F6*E6+F7*E7)*E16</f>
         <v>110.57699361748953</v>
       </c>
-      <c r="H16" s="20"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
+      <c r="H16" s="21"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
     </row>
     <row r="17" spans="2:14">
       <c r="C17" s="3"/>
@@ -4858,10 +4838,10 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
     </row>
     <row r="18" spans="2:14">
       <c r="C18" s="3"/>
@@ -4870,10 +4850,10 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
     </row>
     <row r="19" spans="2:14">
       <c r="C19" s="4" t="s">
@@ -4884,30 +4864,30 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="22"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
     </row>
     <row r="20" spans="2:14" ht="31.5" customHeight="1">
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="16">
         <f>C5*D5+C6*D6+C7*D7</f>
         <v>430</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="18">
+      <c r="D20" s="17"/>
+      <c r="E20" s="16">
         <f>E5*F5+E6*F6+E7*F7</f>
         <v>396.25</v>
       </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="18">
+      <c r="F20" s="17"/>
+      <c r="G20" s="16">
         <f>G5*H5+G6*H6+G7*H7</f>
         <v>335</v>
       </c>
-      <c r="H20" s="19"/>
+      <c r="H20" s="17"/>
       <c r="J20" s="15" t="s">
         <v>22</v>
       </c>
@@ -4916,86 +4896,109 @@
       <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="16">
         <f>C5*D5+C6*D6+C7*D7</f>
         <v>430</v>
       </c>
-      <c r="D21" s="19"/>
-      <c r="E21" s="18">
+      <c r="D21" s="17"/>
+      <c r="E21" s="16">
         <f>E5*D5+E6*D6+E7*D7</f>
         <v>379</v>
       </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="18">
+      <c r="F21" s="17"/>
+      <c r="G21" s="16">
         <f>G5*D5+G6*D6+G7*D7</f>
         <v>457</v>
       </c>
-      <c r="H21" s="19"/>
+      <c r="H21" s="17"/>
       <c r="J21" s="15"/>
     </row>
     <row r="22" spans="2:14" ht="45.5" customHeight="1">
       <c r="B22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="18">
         <f>C20/C21*100</f>
         <v>100</v>
       </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="16">
+      <c r="D22" s="19"/>
+      <c r="E22" s="18">
         <f>E20/E21*100</f>
         <v>104.55145118733509</v>
       </c>
-      <c r="F22" s="17"/>
-      <c r="G22" s="16">
+      <c r="F22" s="19"/>
+      <c r="G22" s="18">
         <f>G20/G21*100</f>
         <v>73.304157549234134</v>
       </c>
-      <c r="H22" s="17"/>
+      <c r="H22" s="19"/>
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="2:14">
       <c r="B23" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="16">
         <f>C5*F5+C6*F6+C7*F7</f>
         <v>577.5</v>
       </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="18">
+      <c r="D23" s="17"/>
+      <c r="E23" s="16">
         <f>E5*F5+E6*F6+E7*F7</f>
         <v>396.25</v>
       </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="18">
+      <c r="F23" s="17"/>
+      <c r="G23" s="16">
         <f>G5*F5+G6*F6+G7*F7</f>
         <v>420</v>
       </c>
-      <c r="H23" s="19"/>
+      <c r="H23" s="17"/>
     </row>
     <row r="24" spans="2:14">
       <c r="B24" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="22">
         <f>C23/C20*100</f>
         <v>134.30232558139534</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="13">
+      <c r="D24" s="23"/>
+      <c r="E24" s="22">
         <f>E23/E20*100</f>
         <v>100</v>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="13">
+      <c r="F24" s="23"/>
+      <c r="G24" s="22">
         <f>G23/G20*100</f>
         <v>125.37313432835822</v>
       </c>
-      <c r="H24" s="14"/>
+      <c r="H24" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="J20:J22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="K10:N19"/>
     <mergeCell ref="J10:J12"/>
     <mergeCell ref="C10:D10"/>
@@ -5012,29 +5015,6 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="J20:J22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370000000000011" bottom="0.39370000000000011" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/exercices/exercice_indices_prix.xlsx
+++ b/exercices/exercice_indices_prix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E80720-9E04-493F-90D8-6BF6D0D397C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6DD3D7-7662-40DE-A67E-35E963E061B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{4B094D14-38C3-40CB-84C2-D4E41A726E94}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{4B094D14-38C3-40CB-84C2-D4E41A726E94}"/>
   </bookViews>
   <sheets>
     <sheet name="EXERCICE" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="22">
   <si>
     <t>Understanding national accounts (ocde), exercice 1 chapitre 2</t>
   </si>
@@ -79,12 +79,6 @@
   </si>
   <si>
     <t>Indice base période 2</t>
-  </si>
-  <si>
-    <t>comptes aux quantités de l'année t-1</t>
-  </si>
-  <si>
-    <t>na</t>
   </si>
   <si>
     <t>Indice en chaine base periode 1</t>
@@ -484,20 +478,20 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1287,8 +1281,8 @@
       <xdr:rowOff>231385</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3116532" cy="418778"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="ZoneTexte 17">
@@ -1554,7 +1548,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="18" name="ZoneTexte 17">
@@ -1628,8 +1622,8 @@
       <xdr:rowOff>88488</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3011249" cy="749712"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="ZoneTexte 18">
@@ -1911,7 +1905,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="19" name="ZoneTexte 18">
@@ -2325,13 +2319,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>52388</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>52388</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>723900</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>11113</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2405,14 +2399,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>90488</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>754063</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2819,7 +2813,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1024660</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>153939</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="779317" cy="470943"/>
@@ -3140,13 +3134,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1426893</xdr:colOff>
+      <xdr:colOff>671949</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>231385</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2107243" cy="418778"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="3349719" cy="418778"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="ZoneTexte 4">
@@ -3160,8 +3154,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="13113335" y="2151039"/>
-              <a:ext cx="2107243" cy="418778"/>
+              <a:off x="12348893" y="2164607"/>
+              <a:ext cx="3349719" cy="418778"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3188,13 +3182,23 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:r>
+                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:t>IC(L)_2/1 = </a:t>
+              </a:r>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:f>
                     <m:fPr>
                       <m:ctrlPr>
                         <a:rPr lang="fr-CH" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          <a:solidFill>
+                            <a:schemeClr val="tx1"/>
+                          </a:solidFill>
+                          <a:effectLst/>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
                         </a:rPr>
                       </m:ctrlPr>
                     </m:fPr>
@@ -3204,7 +3208,13 @@
                           <m:chr m:val="∑"/>
                           <m:ctrlPr>
                             <a:rPr lang="fr-CH" sz="1100" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                           </m:ctrlPr>
                         </m:naryPr>
@@ -3214,13 +3224,25 @@
                               <m:brk m:alnAt="23"/>
                             </m:rPr>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>𝑖</m:t>
                           </m:r>
                           <m:r>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>=1</m:t>
                           </m:r>
@@ -3228,7 +3250,13 @@
                         <m:sup>
                           <m:r>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>𝑘</m:t>
                           </m:r>
@@ -3238,14 +3266,26 @@
                             <m:sSubPr>
                               <m:ctrlPr>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑝</m:t>
                               </m:r>
@@ -3253,13 +3293,25 @@
                             <m:sub>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>=2</m:t>
                               </m:r>
@@ -3269,14 +3321,26 @@
                             <m:sSubPr>
                               <m:ctrlPr>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑞</m:t>
                               </m:r>
@@ -3284,13 +3348,25 @@
                             <m:sub>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>=1</m:t>
                               </m:r>
@@ -3305,7 +3381,13 @@
                           <m:chr m:val="∑"/>
                           <m:ctrlPr>
                             <a:rPr lang="fr-CH" sz="1100" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                           </m:ctrlPr>
                         </m:naryPr>
@@ -3315,13 +3397,25 @@
                               <m:brk m:alnAt="23"/>
                             </m:rPr>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>𝑖</m:t>
                           </m:r>
                           <m:r>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>=1</m:t>
                           </m:r>
@@ -3329,7 +3423,13 @@
                         <m:sup>
                           <m:r>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>𝑘</m:t>
                           </m:r>
@@ -3339,14 +3439,26 @@
                             <m:sSubPr>
                               <m:ctrlPr>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑝</m:t>
                               </m:r>
@@ -3354,13 +3466,25 @@
                             <m:sub>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>=1</m:t>
                               </m:r>
@@ -3370,14 +3494,26 @@
                             <m:sSubPr>
                               <m:ctrlPr>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑞</m:t>
                               </m:r>
@@ -3385,13 +3521,25 @@
                             <m:sub>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>=1</m:t>
                               </m:r>
@@ -3404,15 +3552,23 @@
                 </m:oMath>
               </a14:m>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
-                <a:t> *100 = IC(L)_2/1</a:t>
+                <a:rPr lang="fr-CH" sz="1100">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t> *100</a:t>
               </a:r>
               <a:endParaRPr lang="LID4096" sz="1100"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="ZoneTexte 4">
@@ -3426,8 +3582,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="13113335" y="2151039"/>
-              <a:ext cx="2107243" cy="418778"/>
+              <a:off x="12348893" y="2164607"/>
+              <a:ext cx="3349719" cy="418778"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3454,22 +3610,45 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
+              <a:r>
+                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:t>IC(L)_2/1 = </a:t>
+              </a:r>
               <a:r>
                 <a:rPr lang="fr-CH" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
                 </a:rPr>
                 <a:t>(∑</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="fr-CH" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
                 </a:rPr>
                 <a:t>_(𝑖=1)^𝑘▒〖𝑝_(𝑖𝑡=2) 𝑞_(𝑖𝑡=1) 〗)/(∑_(𝑖=1)^𝑘▒〖𝑝_(𝑖𝑡=1) 𝑞_(𝑖𝑡=1) 〗)</a:t>
               </a:r>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
-                <a:t> *100 = IC(L)_2/1</a:t>
+                <a:rPr lang="fr-CH" sz="1100">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:rPr>
+                <a:t> *100</a:t>
               </a:r>
               <a:endParaRPr lang="LID4096" sz="1100"/>
             </a:p>
@@ -3487,8 +3666,8 @@
       <xdr:rowOff>82138</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2107243" cy="418778"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="ZoneTexte 6">
@@ -3530,13 +3709,23 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:r>
+                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:t>IC(L)_3/1 = </a:t>
+              </a:r>
               <a14:m>
                 <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:f>
                     <m:fPr>
                       <m:ctrlPr>
                         <a:rPr lang="fr-CH" sz="1100" i="1">
-                          <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          <a:solidFill>
+                            <a:schemeClr val="tx1"/>
+                          </a:solidFill>
+                          <a:effectLst/>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
                         </a:rPr>
                       </m:ctrlPr>
                     </m:fPr>
@@ -3546,7 +3735,13 @@
                           <m:chr m:val="∑"/>
                           <m:ctrlPr>
                             <a:rPr lang="fr-CH" sz="1100" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                           </m:ctrlPr>
                         </m:naryPr>
@@ -3556,13 +3751,25 @@
                               <m:brk m:alnAt="23"/>
                             </m:rPr>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>𝑖</m:t>
                           </m:r>
                           <m:r>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>=1</m:t>
                           </m:r>
@@ -3570,7 +3777,13 @@
                         <m:sup>
                           <m:r>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>𝑘</m:t>
                           </m:r>
@@ -3580,14 +3793,26 @@
                             <m:sSubPr>
                               <m:ctrlPr>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑝</m:t>
                               </m:r>
@@ -3595,13 +3820,25 @@
                             <m:sub>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>=3</m:t>
                               </m:r>
@@ -3611,14 +3848,26 @@
                             <m:sSubPr>
                               <m:ctrlPr>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑞</m:t>
                               </m:r>
@@ -3626,13 +3875,25 @@
                             <m:sub>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>=2</m:t>
                               </m:r>
@@ -3647,7 +3908,13 @@
                           <m:chr m:val="∑"/>
                           <m:ctrlPr>
                             <a:rPr lang="fr-CH" sz="1100" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                           </m:ctrlPr>
                         </m:naryPr>
@@ -3657,13 +3924,25 @@
                               <m:brk m:alnAt="23"/>
                             </m:rPr>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>𝑖</m:t>
                           </m:r>
                           <m:r>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>=1</m:t>
                           </m:r>
@@ -3671,7 +3950,13 @@
                         <m:sup>
                           <m:r>
                             <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                              <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              <a:solidFill>
+                                <a:schemeClr val="tx1"/>
+                              </a:solidFill>
+                              <a:effectLst/>
+                              <a:latin typeface="+mn-lt"/>
+                              <a:ea typeface="+mn-ea"/>
+                              <a:cs typeface="+mn-cs"/>
                             </a:rPr>
                             <m:t>𝑘</m:t>
                           </m:r>
@@ -3681,14 +3966,26 @@
                             <m:sSubPr>
                               <m:ctrlPr>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑝</m:t>
                               </m:r>
@@ -3696,13 +3993,25 @@
                             <m:sub>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>=2</m:t>
                               </m:r>
@@ -3712,14 +4021,26 @@
                             <m:sSubPr>
                               <m:ctrlPr>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                               </m:ctrlPr>
                             </m:sSubPr>
                             <m:e>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑞</m:t>
                               </m:r>
@@ -3727,13 +4048,25 @@
                             <m:sub>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>𝑖𝑡</m:t>
                               </m:r>
                               <m:r>
                                 <a:rPr lang="fr-CH" sz="1100" b="0" i="1">
-                                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  <a:solidFill>
+                                    <a:schemeClr val="tx1"/>
+                                  </a:solidFill>
+                                  <a:effectLst/>
+                                  <a:latin typeface="+mn-lt"/>
+                                  <a:ea typeface="+mn-ea"/>
+                                  <a:cs typeface="+mn-cs"/>
                                 </a:rPr>
                                 <m:t>=2</m:t>
                               </m:r>
@@ -3746,10 +4079,6 @@
                 </m:oMath>
               </a14:m>
               <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
-                <a:t> *</a:t>
-              </a:r>
-              <a:r>
                 <a:rPr lang="fr-CH" sz="1100">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
@@ -3759,18 +4088,14 @@
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:rPr>
-                <a:t>IC(L)_2/1</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
-                <a:t> = IC(L)_3/1</a:t>
+                <a:t> *IC(L)_2/1 </a:t>
               </a:r>
               <a:endParaRPr lang="LID4096" sz="1100"/>
             </a:p>
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="ZoneTexte 6">
@@ -3812,22 +4137,33 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
+              <a:r>
+                <a:rPr lang="fr-CH" sz="1100"/>
+                <a:t>IC(L)_3/1 = </a:t>
+              </a:r>
               <a:r>
                 <a:rPr lang="fr-CH" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
                 </a:rPr>
                 <a:t>(∑</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="fr-CH" sz="1100" b="0" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:effectLst/>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
                 </a:rPr>
                 <a:t>_(𝑖=1)^𝑘▒〖𝑝_(𝑖𝑡=3) 𝑞_(𝑖𝑡=2) 〗)/(∑_(𝑖=1)^𝑘▒〖𝑝_(𝑖𝑡=2) 𝑞_(𝑖𝑡=2) 〗)</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
-                <a:t> *</a:t>
               </a:r>
               <a:r>
                 <a:rPr lang="fr-CH" sz="1100">
@@ -3839,11 +4175,7 @@
                   <a:ea typeface="+mn-ea"/>
                   <a:cs typeface="+mn-cs"/>
                 </a:rPr>
-                <a:t>IC(L)_2/1</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr lang="fr-CH" sz="1100"/>
-                <a:t> = IC(L)_3/1</a:t>
+                <a:t> *IC(L)_2/1 </a:t>
               </a:r>
               <a:endParaRPr lang="LID4096" sz="1100"/>
             </a:p>
@@ -4286,37 +4618,37 @@
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="14"/>
       <c r="J10" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" ht="34.5" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14"/>
       <c r="J11" s="15"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" ht="46" customHeight="1">
       <c r="B12" s="6" t="s">
@@ -4329,26 +4661,26 @@
       <c r="G12" s="18"/>
       <c r="H12" s="19"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="14"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="12" t="s">
@@ -4360,14 +4692,14 @@
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
       <c r="H14" s="20"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -4375,10 +4707,10 @@
       <c r="F15" s="21"/>
       <c r="G15" s="21"/>
       <c r="H15" s="21"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14">
       <c r="C16" s="3"/>
@@ -4387,10 +4719,10 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
     </row>
     <row r="17" spans="2:14">
       <c r="C17" s="3"/>
@@ -4399,52 +4731,52 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
     </row>
     <row r="18" spans="2:14">
       <c r="C18" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
     </row>
     <row r="19" spans="2:14">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="17"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
     </row>
     <row r="20" spans="2:14" ht="31.5" customHeight="1">
       <c r="B20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="17"/>
+        <v>17</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="14"/>
       <c r="J20" s="15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="2:14" ht="29.5" customHeight="1">
@@ -4461,14 +4793,14 @@
     </row>
     <row r="22" spans="2:14" ht="45.5" customHeight="1">
       <c r="B22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="17"/>
+        <v>18</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14"/>
       <c r="J22" s="15"/>
     </row>
     <row r="23" spans="2:14">
@@ -4484,6 +4816,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="J20:J22"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="G10:H10"/>
@@ -4500,26 +4852,6 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="J20:J22"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4528,7 +4860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB37D87-4114-4768-9854-07DA7BBB678F}">
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.6328125" customWidth="1"/>
@@ -4661,55 +4993,55 @@
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="13">
         <f>C5*D5+C6*D6+C7*D7</f>
         <v>430</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="16">
+      <c r="D10" s="14"/>
+      <c r="E10" s="13">
         <f>E5*F5+E6*F6+E7*F7</f>
         <v>396.25</v>
       </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="16">
+      <c r="F10" s="14"/>
+      <c r="G10" s="13">
         <f>G5*H5+G6*H6+G7*H7</f>
         <v>335</v>
       </c>
-      <c r="H10" s="17"/>
+      <c r="H10" s="14"/>
       <c r="J10" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" ht="34.5" customHeight="1">
       <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="13">
         <f>C5*D5+C6*D6+C7*D7</f>
         <v>430</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="16">
+      <c r="D11" s="14"/>
+      <c r="E11" s="13">
         <f>C5*F5+C6*F6+C7*F7</f>
         <v>577.5</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="16">
+      <c r="F11" s="14"/>
+      <c r="G11" s="13">
         <f>C5*H5+C6*H6+C7*H7</f>
         <v>497.5</v>
       </c>
-      <c r="H11" s="17"/>
+      <c r="H11" s="14"/>
       <c r="J11" s="15"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" ht="46" customHeight="1">
       <c r="B12" s="6" t="s">
@@ -4731,35 +5063,35 @@
       </c>
       <c r="H12" s="19"/>
       <c r="J12" s="15"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="13">
         <f>E5*D5+E6*D6+E7*D7</f>
         <v>379</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="16">
+      <c r="D13" s="14"/>
+      <c r="E13" s="13">
         <f>E5*F5+E6*F6+E7*F7</f>
         <v>396.25</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="16">
+      <c r="F13" s="14"/>
+      <c r="G13" s="13">
         <f>E5*H5+E6*H6+E7*H7</f>
         <v>326.25</v>
       </c>
-      <c r="H13" s="17"/>
+      <c r="H13" s="14"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="12" t="s">
@@ -4780,56 +5112,45 @@
         <v>82.33438485804416</v>
       </c>
       <c r="H14" s="20"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>16</v>
+      <c r="C15" s="21">
+        <v>100</v>
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="21">
-        <f>F5*C5+F6*C6+F7*C7</f>
-        <v>577.5</v>
+        <f>((F5*C5+F6*C6+F7*C7)/(D5*C5+D6*C6+D7*C7))*100</f>
+        <v>134.30232558139534</v>
       </c>
       <c r="F15" s="21"/>
       <c r="G15" s="21">
-        <f>H5*E5+H6*E6+H7*E7</f>
-        <v>326.25</v>
+        <f>(H5*E5+H6*E6+H7*E7)/(F5*E5+F6*E6+F7*E7)*E15</f>
+        <v>110.57699361748953</v>
       </c>
       <c r="H15" s="21"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="B16" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="21">
-        <v>100</v>
-      </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21">
-        <f>((F5*C5+F6*C6+F7*C7)/(D5*C5+D6*C6+D7*C7))*100</f>
-        <v>134.30232558139534</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21">
-        <f>(H5*E5+H6*E6+H7*E7)/(F5*E5+F6*E6+F7*E7)*E16</f>
-        <v>110.57699361748953</v>
-      </c>
-      <c r="H16" s="21"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
     </row>
     <row r="17" spans="2:14">
       <c r="C17" s="3"/>
@@ -4838,168 +5159,133 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
     </row>
     <row r="18" spans="2:14">
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
+      <c r="C18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
     </row>
-    <row r="19" spans="2:14">
-      <c r="C19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-    </row>
-    <row r="20" spans="2:14" ht="31.5" customHeight="1">
-      <c r="B20" s="5" t="s">
+    <row r="19" spans="2:14" ht="31.5" customHeight="1">
+      <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C19" s="13">
         <f>C5*D5+C6*D6+C7*D7</f>
         <v>430</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="16">
+      <c r="D19" s="14"/>
+      <c r="E19" s="13">
         <f>E5*F5+E6*F6+E7*F7</f>
         <v>396.25</v>
       </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="16">
+      <c r="F19" s="14"/>
+      <c r="G19" s="13">
         <f>G5*H5+G6*H6+G7*H7</f>
         <v>335</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="J20" s="15" t="s">
-        <v>22</v>
+      <c r="H19" s="14"/>
+      <c r="J19" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="29.5" customHeight="1">
-      <c r="B21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="16">
+    <row r="20" spans="2:14" ht="29.5" customHeight="1">
+      <c r="B20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="13">
         <f>C5*D5+C6*D6+C7*D7</f>
         <v>430</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="16">
+      <c r="D20" s="14"/>
+      <c r="E20" s="13">
         <f>E5*D5+E6*D6+E7*D7</f>
         <v>379</v>
       </c>
-      <c r="F21" s="17"/>
-      <c r="G21" s="16">
+      <c r="F20" s="14"/>
+      <c r="G20" s="13">
         <f>G5*D5+G6*D6+G7*D7</f>
         <v>457</v>
       </c>
-      <c r="H21" s="17"/>
+      <c r="H20" s="14"/>
+      <c r="J20" s="15"/>
+    </row>
+    <row r="21" spans="2:14" ht="45.5" customHeight="1">
+      <c r="B21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="18">
+        <f>C19/C20*100</f>
+        <v>100</v>
+      </c>
+      <c r="D21" s="19"/>
+      <c r="E21" s="18">
+        <f>E19/E20*100</f>
+        <v>104.55145118733509</v>
+      </c>
+      <c r="F21" s="19"/>
+      <c r="G21" s="18">
+        <f>G19/G20*100</f>
+        <v>73.304157549234134</v>
+      </c>
+      <c r="H21" s="19"/>
       <c r="J21" s="15"/>
     </row>
-    <row r="22" spans="2:14" ht="45.5" customHeight="1">
-      <c r="B22" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="18">
-        <f>C20/C21*100</f>
-        <v>100</v>
-      </c>
-      <c r="D22" s="19"/>
-      <c r="E22" s="18">
-        <f>E20/E21*100</f>
-        <v>104.55145118733509</v>
-      </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="18">
-        <f>G20/G21*100</f>
-        <v>73.304157549234134</v>
-      </c>
-      <c r="H22" s="19"/>
-      <c r="J22" s="15"/>
+    <row r="22" spans="2:14">
+      <c r="B22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="13">
+        <f>C5*F5+C6*F6+C7*F7</f>
+        <v>577.5</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="13">
+        <f>E5*F5+E6*F6+E7*F7</f>
+        <v>396.25</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="13">
+        <f>G5*F5+G6*F6+G7*F7</f>
+        <v>420</v>
+      </c>
+      <c r="H22" s="14"/>
     </row>
     <row r="23" spans="2:14">
-      <c r="B23" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="16">
-        <f>C5*F5+C6*F6+C7*F7</f>
-        <v>577.5</v>
-      </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="16">
-        <f>E5*F5+E6*F6+E7*F7</f>
-        <v>396.25</v>
-      </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="16">
-        <f>G5*F5+G6*F6+G7*F7</f>
-        <v>420</v>
-      </c>
-      <c r="H23" s="17"/>
-    </row>
-    <row r="24" spans="2:14">
-      <c r="B24" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="22">
-        <f>C23/C20*100</f>
-        <v>134.30232558139534</v>
-      </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="22">
-        <f>E23/E20*100</f>
+      <c r="C23" s="22">
+        <f>C19/C22*100</f>
+        <v>74.458874458874462</v>
+      </c>
+      <c r="D23" s="23"/>
+      <c r="E23" s="22">
+        <f>E19/E22*100</f>
         <v>100</v>
       </c>
-      <c r="F24" s="23"/>
-      <c r="G24" s="22">
-        <f>G23/G20*100</f>
-        <v>125.37313432835822</v>
-      </c>
-      <c r="H24" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="22">
+        <f>G19/G22*100</f>
+        <v>79.761904761904773</v>
+      </c>
+      <c r="H23" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="J20:J22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="K10:N19"/>
+  <mergeCells count="36">
+    <mergeCell ref="K10:N18"/>
     <mergeCell ref="J10:J12"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:F10"/>
@@ -5015,6 +5301,26 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0.39370000000000011" bottom="0.39370000000000011" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
